--- a/docs/downloads/05/tbl_lighting_marovoay_ampijoroa.xlsx
+++ b/docs/downloads/05/tbl_lighting_marovoay_ampijoroa.xlsx
@@ -490,12 +490,6 @@
           <t>Marovoay - Tous</t>
         </is>
       </c>
-      <c r="C8">
-        <v>4</v>
-      </c>
-      <c r="D8">
-        <v>0.5</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">

--- a/docs/downloads/05/tbl_lighting_marovoay_ampijoroa.xlsx
+++ b/docs/downloads/05/tbl_lighting_marovoay_ampijoroa.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -391,7 +391,7 @@
         <v>10</v>
       </c>
       <c r="D2">
-        <v>4.3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3">
@@ -409,7 +409,7 @@
         <v>16</v>
       </c>
       <c r="D3">
-        <v>6.9</v>
+        <v>11.2</v>
       </c>
     </row>
     <row r="4">
@@ -420,14 +420,14 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Panneau Solaire En Marche ?</t>
+          <t>Piles</t>
         </is>
       </c>
       <c r="C4">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D4">
-        <v>16.5</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5">
@@ -438,14 +438,14 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Piles</t>
+          <t>Pétrole Lampant</t>
         </is>
       </c>
       <c r="C5">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="D5">
-        <v>21.6</v>
+        <v>53.1</v>
       </c>
     </row>
     <row r="6">
@@ -456,32 +456,21 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Pétrole Lampant</t>
+          <t>Solaire</t>
         </is>
       </c>
       <c r="C6">
-        <v>76</v>
+        <v>41</v>
       </c>
       <c r="D6">
-        <v>32.9</v>
+        <v>28.7</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Solaire</t>
-        </is>
-      </c>
-      <c r="C7">
-        <v>41</v>
-      </c>
-      <c r="D7">
-        <v>17.7</v>
+          <t>Marovoay - Tous</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -490,6 +479,17 @@
           <t>Marovoay - Tous</t>
         </is>
       </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Autres</t>
+        </is>
+      </c>
+      <c r="C8">
+        <v>31</v>
+      </c>
+      <c r="D8">
+        <v>6</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -499,14 +499,14 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Autres</t>
+          <t>Batteries</t>
         </is>
       </c>
       <c r="C9">
-        <v>31</v>
+        <v>65</v>
       </c>
       <c r="D9">
-        <v>3.6</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="10">
@@ -517,14 +517,14 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Batteries</t>
+          <t>Bois De Chauffe</t>
         </is>
       </c>
       <c r="C10">
-        <v>65</v>
+        <v>6</v>
       </c>
       <c r="D10">
-        <v>7.5</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="11">
@@ -535,14 +535,14 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Bois De Chauffe</t>
+          <t>Piles</t>
         </is>
       </c>
       <c r="C11">
-        <v>6</v>
+        <v>151</v>
       </c>
       <c r="D11">
-        <v>0.7</v>
+        <v>29.1</v>
       </c>
     </row>
     <row r="12">
@@ -553,14 +553,14 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Panneau Solaire En Marche ?</t>
+          <t>Pétrole Lampant</t>
         </is>
       </c>
       <c r="C12">
-        <v>163</v>
+        <v>283</v>
       </c>
       <c r="D12">
-        <v>18.8</v>
+        <v>54.5</v>
       </c>
     </row>
     <row r="13">
@@ -571,50 +571,14 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Piles</t>
+          <t>Solaire</t>
         </is>
       </c>
       <c r="C13">
-        <v>151</v>
+        <v>162</v>
       </c>
       <c r="D13">
-        <v>17.5</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Marovoay - Tous</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Pétrole Lampant</t>
-        </is>
-      </c>
-      <c r="C14">
-        <v>283</v>
-      </c>
-      <c r="D14">
-        <v>32.7</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Marovoay - Tous</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Solaire</t>
-        </is>
-      </c>
-      <c r="C15">
-        <v>162</v>
-      </c>
-      <c r="D15">
-        <v>18.7</v>
+        <v>31.2</v>
       </c>
     </row>
   </sheetData>
